--- a/常見的AI應用/office辦公室應用進階的對齊/報價單_示範成果_客戶3_好日子生活選物.xlsx
+++ b/常見的AI應用/office辦公室應用進階的對齊/報價單_示範成果_客戶3_好日子生活選物.xlsx
@@ -1,10 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="報價單範本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="教學說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -86,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,6 +192,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -467,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A2:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -477,10 +480,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="9" t="inlineStr">
         <is>
@@ -501,7 +502,6 @@
       <c r="F3" s="1" t="n"/>
       <c r="G3" s="1" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="27" customHeight="1">
       <c r="B5" s="13" t="inlineStr">
         <is>
@@ -582,8 +582,6 @@
       <c r="F9" s="1" t="n"/>
       <c r="G9" s="1" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -617,6 +615,7 @@
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" s="24" t="n">
         <v>1</v>
       </c>
@@ -642,7 +641,8 @@
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="B14" t="n">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="24" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -662,11 +662,12 @@
         <v>4200</v>
       </c>
       <c r="G14" s="49">
-        <f>IF(AND(ISNUMBER(D14),ISNUMBER(F14)),D14*F14,"待填資料")</f>
+        <f>IF(AND(ISNUMBER(D13),ISNUMBER(F13)),D13*F13,"待填資料")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" s="24" t="n">
         <v>3</v>
       </c>
@@ -687,57 +688,67 @@
         <v>18000</v>
       </c>
       <c r="G15" s="49">
-        <f>IF(AND(ISNUMBER(D15),ISNUMBER(F15)),D15*F15,"待填資料")</f>
+        <f>IF(AND(ISNUMBER(D13),ISNUMBER(F13)),D13*F13,"待填資料")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="F16" s="29" t="n"/>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="53" t="n"/>
       <c r="G16" s="49" t="n"/>
     </row>
-    <row r="17">
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="49" t="n"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>未稅合計</t>
+        </is>
+      </c>
+      <c r="G17" s="50">
+        <f>SUM(G13:G14)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>未稅合計</t>
+          <t>營業稅 5%</t>
         </is>
       </c>
       <c r="G18" s="50">
-        <f>SUM(G13:G15)</f>
+        <f>G15*5%</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="F19" s="30" t="inlineStr">
-        <is>
-          <t>營業稅 5%</t>
-        </is>
-      </c>
-      <c r="G19" s="50">
-        <f>G18*5%</f>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>含稅總計</t>
+        </is>
+      </c>
+      <c r="G19" s="51">
+        <f>G15+G16</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="F20" s="31" t="inlineStr">
-        <is>
-          <t>含稅總計</t>
-        </is>
-      </c>
-      <c r="G20" s="51">
-        <f>G18+G19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="B23" s="22" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>專案備註與付款條件</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>資料來源由客戶提供；含兩次修改與一次成果說明會。</t>
         </is>
       </c>
       <c r="C23" s="1" t="n"/>
@@ -747,175 +758,49 @@
       <c r="G23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="45" t="inlineStr">
-        <is>
-          <t>資料來源由客戶提供；含兩次修改與一次成果說明會。</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
+      <c r="B24" s="1" t="n"/>
       <c r="G24" s="1" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="26" customHeight="1">
       <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
+      <c r="D25" s="1" t="n"/>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
       <c r="G25" s="1" t="n"/>
     </row>
-    <row r="26">
-      <c r="B26" s="1" t="n"/>
-      <c r="C26" s="1" t="n"/>
-      <c r="D26" s="1" t="n"/>
-      <c r="E26" s="1" t="n"/>
-      <c r="F26" s="1" t="n"/>
-      <c r="G26" s="1" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="1" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>報價有效期限：2026/11/10</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
-      <c r="F29" s="1" t="n"/>
-      <c r="G29" s="1" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="47" t="inlineStr">
-        <is>
-          <t>教學重點：黃色為佔位符｜藍色為公式｜請保留儲存格格式與公式</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
+      <c r="E28" s="1" t="n"/>
+      <c r="F28" s="1" t="n"/>
+      <c r="G28" s="1" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="47" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B2:G3"/>
-    <mergeCell ref="B24:G26"/>
     <mergeCell ref="D9:G9"/>
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D6:G6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B31:G31"/>
     <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B23:G25"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>課堂實作流程</t>
-        </is>
-      </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. 觀察範本</t>
-        </is>
-      </c>
-      <c r="B2" s="48" t="inlineStr">
-        <is>
-          <t>黃色儲存格使用 {{欄位名稱}} 作為佔位符。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. 準備資料</t>
-        </is>
-      </c>
-      <c r="B3" s="48" t="inlineStr">
-        <is>
-          <t>由老師提供客戶報價資料（Markdown 或 TXT）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3. AI 替換</t>
-        </is>
-      </c>
-      <c r="B4" s="48" t="inlineStr">
-        <is>
-          <t>請 AI 依欄位名稱替換，保留樣式、合併儲存格與公式。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. 公式計算</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>數量與單價必須轉為數字，小計及總計自動計算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5. 檢查對齊</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>觀察文字置中、靠左、數字靠右及長文字換行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6. 進階挑戰</t>
-        </is>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>一份範本產生多位客戶的報價單。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/常見的AI應用/office辦公室應用進階的對齊/報價單_示範成果_客戶3_好日子生活選物.xlsx
+++ b/常見的AI應用/office辦公室應用進階的對齊/報價單_示範成果_客戶3_好日子生活選物.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G30"/>
+  <dimension ref="A2:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>需求訪談</t>
+          <t>商業需求訪談與指標定義</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>銷售數據清理</t>
+          <t>跨平台銷售數據清洗與彙整</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>互動式儀表板</t>
+          <t>PowerBI 互動式數據儀表板建置</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
@@ -694,61 +694,75 @@
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="53" t="n"/>
-      <c r="G16" s="49" t="n"/>
+      <c r="B16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>資料庫自動定時更新排程設定</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>式</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G16" s="49">
+        <f>IF(AND(ISNUMBER(D13),ISNUMBER(F13)),D13*F13,"待填資料")</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="F17" s="30" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>未稅合計</t>
         </is>
       </c>
-      <c r="G17" s="50">
+      <c r="G18" s="50">
         <f>SUM(G13:G14)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="F18" s="30" t="inlineStr">
+    <row r="19">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>營業稅 5%</t>
         </is>
       </c>
-      <c r="G18" s="50">
+      <c r="G19" s="50">
         <f>G15*5%</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="F19" s="31" t="inlineStr">
+    <row r="20">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>含稅總計</t>
         </is>
       </c>
-      <c r="G19" s="51">
+      <c r="G20" s="51">
         <f>G15+G16</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="22" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>專案備註與付款條件</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
-      <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="45" t="inlineStr">
-        <is>
-          <t>資料來源由客戶提供；含兩次修改與一次成果說明會。</t>
         </is>
       </c>
       <c r="C23" s="1" t="n"/>
@@ -758,48 +772,60 @@
       <c r="G23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="1" t="n"/>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>資料來源由客戶提供；含兩次修改與一次成果說明會。</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="n"/>
       <c r="G24" s="1" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1">
+    <row r="25">
       <c r="B25" s="1" t="n"/>
-      <c r="C25" s="1" t="n"/>
-      <c r="D25" s="1" t="n"/>
-      <c r="E25" s="1" t="n"/>
-      <c r="F25" s="1" t="n"/>
       <c r="G25" s="1" t="n"/>
     </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="n"/>
+      <c r="D26" s="1" t="n"/>
+      <c r="E26" s="1" t="n"/>
+      <c r="F26" s="1" t="n"/>
+      <c r="G26" s="1" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>報價有效期限：2026/11/10</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
-      <c r="F28" s="1" t="n"/>
-      <c r="G28" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="47" t="n"/>
+      <c r="C29" s="1" t="n"/>
+      <c r="D29" s="1" t="n"/>
+      <c r="E29" s="1" t="n"/>
+      <c r="F29" s="1" t="n"/>
+      <c r="G29" s="1" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B2:G3"/>
     <mergeCell ref="D9:G9"/>
-    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B24:G26"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B22:G22"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D7:G7"/>
-    <mergeCell ref="B23:G25"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
